--- a/Aiden Pro Streamlit 웹 대시보드 구조 및 코드기획.xlsx
+++ b/Aiden Pro Streamlit 웹 대시보드 구조 및 코드기획.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\runia\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\runia\Desktop\Aiden Pro(AI_Data_Enhancer)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9544EC-8E2E-4EE0-A33B-3A9BD9204A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3BC1B1-E7FC-465C-9210-B26482B7D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="650" windowWidth="21530" windowHeight="14320" xr2:uid="{1C5A22F4-6E81-40DC-AF91-00BE1332F187}"/>
+    <workbookView xWindow="4540" yWindow="780" windowWidth="21230" windowHeight="14090" xr2:uid="{1C5A22F4-6E81-40DC-AF91-00BE1332F187}"/>
   </bookViews>
   <sheets>
     <sheet name="Aiden Pro" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>데이터 업로드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,10 +182,6 @@
   </si>
   <si>
     <t>변수 관계 분석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -376,7 +372,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -425,6 +421,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -434,6 +454,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -443,43 +469,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -816,12 +815,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10363E5-9D31-479E-9182-E09679BB27FF}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" style="3" customWidth="1"/>
     <col min="2" max="2" width="21.58203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="2" customWidth="1"/>
     <col min="4" max="5" width="32.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="42" style="2" customWidth="1"/>
@@ -854,7 +853,7 @@
     <row r="2" spans="1:7" s="3" customFormat="1" ht="69" thickTop="1" thickBot="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="13"/>
@@ -868,10 +867,10 @@
       <c r="A3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="17" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -886,13 +885,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="32" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -905,9 +904,9 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="18"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
@@ -916,9 +915,9 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="18"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
@@ -927,9 +926,9 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="18"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
@@ -938,9 +937,9 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="20"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
@@ -951,9 +950,9 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="9" t="s">
         <v>16</v>
       </c>
@@ -964,11 +963,11 @@
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="26" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="22" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -981,9 +980,9 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
@@ -994,13 +993,13 @@
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="19" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -1013,9 +1012,9 @@
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
@@ -1026,9 +1025,9 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="17"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1039,9 +1038,9 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
       <c r="D15" s="6" t="s">
         <v>16</v>
       </c>
@@ -1052,11 +1051,11 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A16" s="17"/>
-      <c r="B16" s="32" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="19" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -1069,9 +1068,9 @@
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="17"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="5" t="s">
         <v>13</v>
       </c>
@@ -1082,9 +1081,9 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="17"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1095,9 +1094,9 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="18"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="5" t="s">
         <v>16</v>
       </c>
@@ -1106,11 +1105,6 @@
         <v>21</v>
       </c>
       <c r="G19" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="2" t="s">
-        <v>36</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/Aiden Pro Streamlit 웹 대시보드 구조 및 코드기획.xlsx
+++ b/Aiden Pro Streamlit 웹 대시보드 구조 및 코드기획.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\runia\Desktop\Aiden Pro(AI_Data_Enhancer)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3BC1B1-E7FC-465C-9210-B26482B7D205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32314EEA-3074-44D8-BDD5-7C7A9ECE38DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="780" windowWidth="21230" windowHeight="14090" xr2:uid="{1C5A22F4-6E81-40DC-AF91-00BE1332F187}"/>
+    <workbookView xWindow="5530" yWindow="1980" windowWidth="19780" windowHeight="12860" xr2:uid="{1C5A22F4-6E81-40DC-AF91-00BE1332F187}"/>
   </bookViews>
   <sheets>
     <sheet name="Aiden Pro" sheetId="1" r:id="rId1"/>
@@ -445,6 +445,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -468,18 +480,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -885,13 +885,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -904,9 +904,9 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="26"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
@@ -915,9 +915,9 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="26"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
@@ -926,9 +926,9 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="26"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
@@ -937,9 +937,9 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="30"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
@@ -950,9 +950,9 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="9" t="s">
         <v>16</v>
       </c>
@@ -963,7 +963,7 @@
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A10" s="30"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="21" t="s">
         <v>12</v>
       </c>
@@ -980,8 +980,8 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A11" s="31"/>
-      <c r="B11" s="28"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="23"/>
       <c r="D11" s="6" t="s">
         <v>16</v>
@@ -993,7 +993,7 @@
       <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="19" t="s">
@@ -1012,7 +1012,7 @@
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="25"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="5" t="s">
@@ -1025,7 +1025,7 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="25"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="6" t="s">
@@ -1038,9 +1038,9 @@
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="17.5" thickBot="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
       <c r="D15" s="6" t="s">
         <v>16</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" ht="17.5" thickTop="1">
-      <c r="A16" s="25"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="19" t="s">
         <v>22</v>
       </c>
@@ -1068,7 +1068,7 @@
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="25"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="5" t="s">
@@ -1081,7 +1081,7 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="25"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="6" t="s">
@@ -1094,7 +1094,7 @@
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="26"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
       <c r="D19" s="5" t="s">
